--- a/output/yearly_population_iteration_8_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_8_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6663</v>
+        <v>3639</v>
       </c>
       <c r="C2" t="n">
-        <v>6204</v>
+        <v>17590</v>
       </c>
       <c r="D2" t="n">
-        <v>21171</v>
+        <v>31903</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3903</v>
+        <v>2799</v>
       </c>
       <c r="C3" t="n">
-        <v>5998</v>
+        <v>5906</v>
       </c>
       <c r="D3" t="n">
-        <v>14377</v>
+        <v>11888</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3082</v>
+        <v>2268</v>
       </c>
       <c r="C4" t="n">
-        <v>4867</v>
+        <v>7284</v>
       </c>
       <c r="D4" t="n">
-        <v>7598</v>
+        <v>5123</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1988</v>
+        <v>1457</v>
       </c>
       <c r="C5" t="n">
-        <v>3835</v>
+        <v>6584</v>
       </c>
       <c r="D5" t="n">
-        <v>2892</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1062</v>
+        <v>805</v>
       </c>
       <c r="C6" t="n">
-        <v>2555</v>
+        <v>4790</v>
       </c>
       <c r="D6" t="n">
-        <v>1208</v>
+        <v>979</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>493</v>
+        <v>376</v>
       </c>
       <c r="C7" t="n">
-        <v>1525</v>
+        <v>2901</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="C8" t="n">
-        <v>702</v>
+        <v>1366</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
+        <v>498</v>
+      </c>
+      <c r="D9" t="n">
         <v>304</v>
-      </c>
-      <c r="D9" t="n">
-        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10109</v>
+        <v>5157</v>
       </c>
       <c r="C2" t="n">
-        <v>9213</v>
+        <v>11878</v>
       </c>
       <c r="D2" t="n">
-        <v>35698</v>
+        <v>33693</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4220</v>
+        <v>2590</v>
       </c>
       <c r="C3" t="n">
-        <v>5352</v>
+        <v>9618</v>
       </c>
       <c r="D3" t="n">
-        <v>14334</v>
+        <v>13670</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2945</v>
+        <v>2128</v>
       </c>
       <c r="C4" t="n">
-        <v>5319</v>
+        <v>6510</v>
       </c>
       <c r="D4" t="n">
-        <v>8400</v>
+        <v>6006</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2178</v>
+        <v>1595</v>
       </c>
       <c r="C5" t="n">
-        <v>4203</v>
+        <v>6686</v>
       </c>
       <c r="D5" t="n">
-        <v>3572</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1343</v>
+        <v>968</v>
       </c>
       <c r="C6" t="n">
-        <v>3119</v>
+        <v>5456</v>
       </c>
       <c r="D6" t="n">
-        <v>1438</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>659</v>
+        <v>489</v>
       </c>
       <c r="C7" t="n">
-        <v>1973</v>
+        <v>3695</v>
       </c>
       <c r="D7" t="n">
-        <v>740</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>274</v>
+        <v>207</v>
       </c>
       <c r="C8" t="n">
-        <v>1064</v>
+        <v>1968</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C9" t="n">
-        <v>468</v>
+        <v>838</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10174</v>
+        <v>5038</v>
       </c>
       <c r="C2" t="n">
-        <v>11156</v>
+        <v>12968</v>
       </c>
       <c r="D2" t="n">
-        <v>30407</v>
+        <v>30229</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5347</v>
+        <v>2878</v>
       </c>
       <c r="C3" t="n">
-        <v>6164</v>
+        <v>9346</v>
       </c>
       <c r="D3" t="n">
-        <v>16128</v>
+        <v>15059</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2982</v>
+        <v>1968</v>
       </c>
       <c r="C4" t="n">
-        <v>5171</v>
+        <v>7565</v>
       </c>
       <c r="D4" t="n">
-        <v>9056</v>
+        <v>6795</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2216</v>
+        <v>1603</v>
       </c>
       <c r="C5" t="n">
-        <v>4557</v>
+        <v>6477</v>
       </c>
       <c r="D5" t="n">
-        <v>4124</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1531</v>
+        <v>1094</v>
       </c>
       <c r="C6" t="n">
-        <v>3548</v>
+        <v>5818</v>
       </c>
       <c r="D6" t="n">
-        <v>1726</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>836</v>
+        <v>597</v>
       </c>
       <c r="C7" t="n">
-        <v>2424</v>
+        <v>4313</v>
       </c>
       <c r="D7" t="n">
-        <v>820</v>
+        <v>710</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>376</v>
+        <v>275</v>
       </c>
       <c r="C8" t="n">
-        <v>1428</v>
+        <v>2574</v>
       </c>
       <c r="D8" t="n">
-        <v>492</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="C9" t="n">
-        <v>691</v>
+        <v>1236</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>325</v>
+        <v>493</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9289</v>
+        <v>4746</v>
       </c>
       <c r="C2" t="n">
-        <v>7496</v>
+        <v>9233</v>
       </c>
       <c r="D2" t="n">
-        <v>24944</v>
+        <v>25050</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5957</v>
+        <v>3417</v>
       </c>
       <c r="C3" t="n">
-        <v>9430</v>
+        <v>13454</v>
       </c>
       <c r="D3" t="n">
-        <v>17558</v>
+        <v>15741</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2047</v>
+        <v>1481</v>
       </c>
       <c r="C4" t="n">
-        <v>7253</v>
+        <v>10139</v>
       </c>
       <c r="D4" t="n">
-        <v>8809</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1414</v>
+        <v>1010</v>
       </c>
       <c r="C5" t="n">
-        <v>3477</v>
+        <v>5701</v>
       </c>
       <c r="D5" t="n">
-        <v>2839</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>772</v>
+        <v>551</v>
       </c>
       <c r="C6" t="n">
-        <v>2375</v>
+        <v>4226</v>
       </c>
       <c r="D6" t="n">
-        <v>803</v>
+        <v>695</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>347</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>1399</v>
+        <v>2522</v>
       </c>
       <c r="D7" t="n">
-        <v>482</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>677</v>
+        <v>1211</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>318</v>
+        <v>483</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5408</v>
+        <v>2884</v>
       </c>
       <c r="C2" t="n">
-        <v>3810</v>
+        <v>4314</v>
       </c>
       <c r="D2" t="n">
-        <v>17507</v>
+        <v>18257</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6345</v>
+        <v>3422</v>
       </c>
       <c r="C3" t="n">
-        <v>7735</v>
+        <v>10593</v>
       </c>
       <c r="D3" t="n">
-        <v>17551</v>
+        <v>16051</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3066</v>
+        <v>1903</v>
       </c>
       <c r="C4" t="n">
-        <v>8335</v>
+        <v>11781</v>
       </c>
       <c r="D4" t="n">
-        <v>10054</v>
+        <v>7588</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1577</v>
+        <v>1120</v>
       </c>
       <c r="C5" t="n">
-        <v>5166</v>
+        <v>7560</v>
       </c>
       <c r="D5" t="n">
-        <v>3552</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>931</v>
+        <v>642</v>
       </c>
       <c r="C6" t="n">
-        <v>2910</v>
+        <v>4912</v>
       </c>
       <c r="D6" t="n">
-        <v>1012</v>
+        <v>813</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>237</v>
       </c>
       <c r="C7" t="n">
-        <v>1775</v>
+        <v>3160</v>
       </c>
       <c r="D7" t="n">
-        <v>527</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="C8" t="n">
-        <v>905</v>
+        <v>1568</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C9" t="n">
-        <v>370</v>
+        <v>503</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5523</v>
+        <v>2557</v>
       </c>
       <c r="C2" t="n">
-        <v>9508</v>
+        <v>6452</v>
       </c>
       <c r="D2" t="n">
-        <v>18462</v>
+        <v>18006</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4995</v>
+        <v>2701</v>
       </c>
       <c r="C3" t="n">
-        <v>5179</v>
+        <v>6979</v>
       </c>
       <c r="D3" t="n">
-        <v>16505</v>
+        <v>15280</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3863</v>
+        <v>2174</v>
       </c>
       <c r="C4" t="n">
-        <v>7862</v>
+        <v>10988</v>
       </c>
       <c r="D4" t="n">
-        <v>10875</v>
+        <v>8657</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1951</v>
+        <v>1277</v>
       </c>
       <c r="C5" t="n">
-        <v>6629</v>
+        <v>9266</v>
       </c>
       <c r="D5" t="n">
-        <v>4505</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1100</v>
+        <v>756</v>
       </c>
       <c r="C6" t="n">
-        <v>3899</v>
+        <v>6033</v>
       </c>
       <c r="D6" t="n">
-        <v>1388</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>497</v>
+        <v>340</v>
       </c>
       <c r="C7" t="n">
-        <v>2292</v>
+        <v>3862</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>1271</v>
+        <v>2191</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>577</v>
+        <v>888</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>275</v>
+        <v>321</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3294</v>
+        <v>1562</v>
       </c>
       <c r="C2" t="n">
-        <v>4351</v>
+        <v>3188</v>
       </c>
       <c r="D2" t="n">
-        <v>12730</v>
+        <v>12704</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4941</v>
+        <v>2579</v>
       </c>
       <c r="C3" t="n">
-        <v>6502</v>
+        <v>6635</v>
       </c>
       <c r="D3" t="n">
-        <v>16328</v>
+        <v>15223</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4247</v>
+        <v>2376</v>
       </c>
       <c r="C4" t="n">
-        <v>7627</v>
+        <v>10621</v>
       </c>
       <c r="D4" t="n">
-        <v>11754</v>
+        <v>9377</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2011</v>
+        <v>1320</v>
       </c>
       <c r="C5" t="n">
-        <v>7833</v>
+        <v>11253</v>
       </c>
       <c r="D5" t="n">
-        <v>4744</v>
+        <v>3181</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>906</v>
+        <v>600</v>
       </c>
       <c r="C6" t="n">
-        <v>4730</v>
+        <v>6882</v>
       </c>
       <c r="D6" t="n">
-        <v>1357</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>2374</v>
+        <v>4006</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C8" t="n">
-        <v>964</v>
+        <v>1471</v>
       </c>
       <c r="D8" t="n">
-        <v>382</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4042</v>
+        <v>1470</v>
       </c>
       <c r="C2" t="n">
-        <v>2853</v>
+        <v>8258</v>
       </c>
       <c r="D2" t="n">
-        <v>14970</v>
+        <v>10338</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3606</v>
+        <v>1871</v>
       </c>
       <c r="C3" t="n">
-        <v>4896</v>
+        <v>4638</v>
       </c>
       <c r="D3" t="n">
-        <v>14741</v>
+        <v>14048</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3999</v>
+        <v>2169</v>
       </c>
       <c r="C4" t="n">
-        <v>7001</v>
+        <v>8639</v>
       </c>
       <c r="D4" t="n">
-        <v>12143</v>
+        <v>9933</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2566</v>
+        <v>1534</v>
       </c>
       <c r="C5" t="n">
-        <v>7652</v>
+        <v>10860</v>
       </c>
       <c r="D5" t="n">
-        <v>5722</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1205</v>
+        <v>769</v>
       </c>
       <c r="C6" t="n">
-        <v>6043</v>
+        <v>8610</v>
       </c>
       <c r="D6" t="n">
-        <v>1794</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>335</v>
+        <v>220</v>
       </c>
       <c r="C7" t="n">
-        <v>3366</v>
+        <v>5153</v>
       </c>
       <c r="D7" t="n">
-        <v>688</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1493</v>
+        <v>2343</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>501</v>
+        <v>663</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2905</v>
+        <v>937</v>
       </c>
       <c r="C2" t="n">
-        <v>1913</v>
+        <v>5599</v>
       </c>
       <c r="D2" t="n">
-        <v>10739</v>
+        <v>9041</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3282</v>
+        <v>1535</v>
       </c>
       <c r="C3" t="n">
-        <v>3753</v>
+        <v>5490</v>
       </c>
       <c r="D3" t="n">
-        <v>13966</v>
+        <v>12890</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3545</v>
+        <v>1924</v>
       </c>
       <c r="C4" t="n">
-        <v>6141</v>
+        <v>7210</v>
       </c>
       <c r="D4" t="n">
-        <v>12239</v>
+        <v>10335</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2846</v>
+        <v>1645</v>
       </c>
       <c r="C5" t="n">
-        <v>7549</v>
+        <v>10221</v>
       </c>
       <c r="D5" t="n">
-        <v>6397</v>
+        <v>4413</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1435</v>
+        <v>872</v>
       </c>
       <c r="C6" t="n">
-        <v>6792</v>
+        <v>9604</v>
       </c>
       <c r="D6" t="n">
-        <v>2147</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>313</v>
+        <v>196</v>
       </c>
       <c r="C7" t="n">
-        <v>4251</v>
+        <v>6249</v>
       </c>
       <c r="D7" t="n">
-        <v>784</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C8" t="n">
-        <v>1937</v>
+        <v>2952</v>
       </c>
       <c r="D8" t="n">
-        <v>416</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>590</v>
+        <v>701</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4088</v>
+        <v>1280</v>
       </c>
       <c r="C2" t="n">
-        <v>4604</v>
+        <v>13775</v>
       </c>
       <c r="D2" t="n">
-        <v>11344</v>
+        <v>8754</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2649</v>
+        <v>1131</v>
       </c>
       <c r="C3" t="n">
-        <v>2706</v>
+        <v>4946</v>
       </c>
       <c r="D3" t="n">
-        <v>12684</v>
+        <v>11654</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3000</v>
+        <v>1562</v>
       </c>
       <c r="C4" t="n">
-        <v>5004</v>
+        <v>6383</v>
       </c>
       <c r="D4" t="n">
-        <v>12115</v>
+        <v>10364</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2841</v>
+        <v>1587</v>
       </c>
       <c r="C5" t="n">
-        <v>6824</v>
+        <v>8881</v>
       </c>
       <c r="D5" t="n">
-        <v>6987</v>
+        <v>5017</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1769</v>
+        <v>1037</v>
       </c>
       <c r="C6" t="n">
-        <v>7025</v>
+        <v>9748</v>
       </c>
       <c r="D6" t="n">
-        <v>2628</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>588</v>
+        <v>348</v>
       </c>
       <c r="C7" t="n">
-        <v>5195</v>
+        <v>7397</v>
       </c>
       <c r="D7" t="n">
-        <v>949</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>2771</v>
+        <v>4045</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>1025</v>
+        <v>1362</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5229</v>
+        <v>4425</v>
       </c>
       <c r="C2" t="n">
-        <v>3077</v>
+        <v>14029</v>
       </c>
       <c r="D2" t="n">
-        <v>12540</v>
+        <v>7527</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2927</v>
+        <v>945</v>
       </c>
       <c r="C2" t="n">
-        <v>2615</v>
+        <v>8265</v>
       </c>
       <c r="D2" t="n">
-        <v>8349</v>
+        <v>6583</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3562</v>
+        <v>1577</v>
       </c>
       <c r="C3" t="n">
-        <v>3380</v>
+        <v>7293</v>
       </c>
       <c r="D3" t="n">
-        <v>13716</v>
+        <v>12403</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4156</v>
+        <v>2264</v>
       </c>
       <c r="C4" t="n">
-        <v>7185</v>
+        <v>9406</v>
       </c>
       <c r="D4" t="n">
-        <v>12493</v>
+        <v>10405</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1713</v>
+        <v>958</v>
       </c>
       <c r="C5" t="n">
-        <v>9962</v>
+        <v>13385</v>
       </c>
       <c r="D5" t="n">
-        <v>6318</v>
+        <v>4456</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>543</v>
+        <v>321</v>
       </c>
       <c r="C6" t="n">
-        <v>6468</v>
+        <v>8873</v>
       </c>
       <c r="D6" t="n">
-        <v>2096</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="C7" t="n">
-        <v>2715</v>
+        <v>3964</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>1004</v>
+        <v>1334</v>
       </c>
       <c r="D8" t="n">
-        <v>300</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6638</v>
+        <v>5655</v>
       </c>
       <c r="C2" t="n">
-        <v>7648</v>
+        <v>8440</v>
       </c>
       <c r="D2" t="n">
-        <v>12486</v>
+        <v>8048</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2222</v>
+        <v>1881</v>
       </c>
       <c r="C3" t="n">
-        <v>1550</v>
+        <v>7070</v>
       </c>
       <c r="D3" t="n">
-        <v>2746</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5360</v>
+        <v>3986</v>
       </c>
       <c r="C2" t="n">
-        <v>5856</v>
+        <v>11354</v>
       </c>
       <c r="D2" t="n">
-        <v>22906</v>
+        <v>12210</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3635</v>
+        <v>3092</v>
       </c>
       <c r="C3" t="n">
-        <v>4358</v>
+        <v>6765</v>
       </c>
       <c r="D3" t="n">
-        <v>4180</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>999</v>
+        <v>851</v>
       </c>
       <c r="C4" t="n">
-        <v>966</v>
+        <v>4186</v>
       </c>
       <c r="D4" t="n">
-        <v>1734</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5175</v>
+        <v>4429</v>
       </c>
       <c r="C2" t="n">
-        <v>4352</v>
+        <v>9778</v>
       </c>
       <c r="D2" t="n">
-        <v>26154</v>
+        <v>12711</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3680</v>
+        <v>2906</v>
       </c>
       <c r="C3" t="n">
-        <v>4479</v>
+        <v>8086</v>
       </c>
       <c r="D3" t="n">
-        <v>6875</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1960</v>
+        <v>1675</v>
       </c>
       <c r="C4" t="n">
-        <v>2867</v>
+        <v>5494</v>
       </c>
       <c r="D4" t="n">
-        <v>2150</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>470</v>
+        <v>403</v>
       </c>
       <c r="C5" t="n">
-        <v>621</v>
+        <v>2385</v>
       </c>
       <c r="D5" t="n">
-        <v>1238</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6400</v>
+        <v>4468</v>
       </c>
       <c r="C2" t="n">
-        <v>5996</v>
+        <v>10824</v>
       </c>
       <c r="D2" t="n">
-        <v>31164</v>
+        <v>24478</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3607</v>
+        <v>2966</v>
       </c>
       <c r="C3" t="n">
-        <v>3841</v>
+        <v>7795</v>
       </c>
       <c r="D3" t="n">
-        <v>9321</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2375</v>
+        <v>1923</v>
       </c>
       <c r="C4" t="n">
-        <v>3646</v>
+        <v>6695</v>
       </c>
       <c r="D4" t="n">
-        <v>2925</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1011</v>
+        <v>854</v>
       </c>
       <c r="C5" t="n">
-        <v>1793</v>
+        <v>3947</v>
       </c>
       <c r="D5" t="n">
-        <v>1366</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="C6" t="n">
-        <v>461</v>
+        <v>1339</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7354</v>
+        <v>5537</v>
       </c>
       <c r="C2" t="n">
-        <v>8098</v>
+        <v>12028</v>
       </c>
       <c r="D2" t="n">
-        <v>25689</v>
+        <v>22123</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3651</v>
+        <v>2672</v>
       </c>
       <c r="C3" t="n">
-        <v>4048</v>
+        <v>7634</v>
       </c>
       <c r="D3" t="n">
-        <v>11274</v>
+        <v>7244</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1844</v>
+        <v>1497</v>
       </c>
       <c r="C4" t="n">
-        <v>3047</v>
+        <v>5964</v>
       </c>
       <c r="D4" t="n">
-        <v>3469</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>879</v>
+        <v>722</v>
       </c>
       <c r="C5" t="n">
-        <v>2028</v>
+        <v>3872</v>
       </c>
       <c r="D5" t="n">
-        <v>1304</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>305</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>759</v>
+        <v>1769</v>
       </c>
       <c r="D6" t="n">
-        <v>779</v>
+        <v>752</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>260</v>
+        <v>523</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5770</v>
+        <v>4488</v>
       </c>
       <c r="C2" t="n">
-        <v>6680</v>
+        <v>7763</v>
       </c>
       <c r="D2" t="n">
-        <v>27220</v>
+        <v>21397</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4580</v>
+        <v>3418</v>
       </c>
       <c r="C3" t="n">
-        <v>5545</v>
+        <v>8750</v>
       </c>
       <c r="D3" t="n">
-        <v>12963</v>
+        <v>9210</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2402</v>
+        <v>1798</v>
       </c>
       <c r="C4" t="n">
-        <v>3598</v>
+        <v>6833</v>
       </c>
       <c r="D4" t="n">
-        <v>5011</v>
+        <v>3206</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1223</v>
+        <v>984</v>
       </c>
       <c r="C5" t="n">
-        <v>2592</v>
+        <v>4996</v>
       </c>
       <c r="D5" t="n">
-        <v>1700</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>552</v>
+        <v>444</v>
       </c>
       <c r="C6" t="n">
-        <v>1480</v>
+        <v>2918</v>
       </c>
       <c r="D6" t="n">
-        <v>861</v>
+        <v>810</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="C7" t="n">
-        <v>543</v>
+        <v>1206</v>
       </c>
       <c r="D7" t="n">
         <v>559</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>241</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
         <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5284</v>
+        <v>3577</v>
       </c>
       <c r="C2" t="n">
-        <v>8396</v>
+        <v>6278</v>
       </c>
       <c r="D2" t="n">
-        <v>21384</v>
+        <v>25628</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4259</v>
+        <v>3230</v>
       </c>
       <c r="C3" t="n">
-        <v>5335</v>
+        <v>7151</v>
       </c>
       <c r="D3" t="n">
-        <v>14310</v>
+        <v>10414</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3015</v>
+        <v>2195</v>
       </c>
       <c r="C4" t="n">
-        <v>4644</v>
+        <v>7739</v>
       </c>
       <c r="D4" t="n">
-        <v>6337</v>
+        <v>4172</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1581</v>
+        <v>1213</v>
       </c>
       <c r="C5" t="n">
-        <v>3098</v>
+        <v>5862</v>
       </c>
       <c r="D5" t="n">
-        <v>2284</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>811</v>
+        <v>633</v>
       </c>
       <c r="C6" t="n">
-        <v>2060</v>
+        <v>3914</v>
       </c>
       <c r="D6" t="n">
-        <v>1001</v>
+        <v>873</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>322</v>
+        <v>259</v>
       </c>
       <c r="C7" t="n">
-        <v>1033</v>
+        <v>2077</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>397</v>
+        <v>784</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>225</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_8_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_8_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3639</v>
+        <v>6512</v>
       </c>
       <c r="C2" t="n">
-        <v>17590</v>
+        <v>5768</v>
       </c>
       <c r="D2" t="n">
-        <v>31903</v>
+        <v>23958</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2799</v>
+        <v>3849</v>
       </c>
       <c r="C3" t="n">
-        <v>5906</v>
+        <v>6393</v>
       </c>
       <c r="D3" t="n">
-        <v>11888</v>
+        <v>12125</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2268</v>
+        <v>2942</v>
       </c>
       <c r="C4" t="n">
-        <v>7284</v>
+        <v>5100</v>
       </c>
       <c r="D4" t="n">
-        <v>5123</v>
+        <v>6156</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1457</v>
+        <v>1968</v>
       </c>
       <c r="C5" t="n">
-        <v>6584</v>
+        <v>4405</v>
       </c>
       <c r="D5" t="n">
-        <v>1954</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>805</v>
+        <v>1105</v>
       </c>
       <c r="C6" t="n">
-        <v>4790</v>
+        <v>2830</v>
       </c>
       <c r="D6" t="n">
-        <v>979</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>376</v>
+        <v>502</v>
       </c>
       <c r="C7" t="n">
-        <v>2901</v>
+        <v>1521</v>
       </c>
       <c r="D7" t="n">
-        <v>634</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="C8" t="n">
-        <v>1366</v>
+        <v>650</v>
       </c>
       <c r="D8" t="n">
-        <v>421</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>498</v>
+        <v>295</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5157</v>
+        <v>9681</v>
       </c>
       <c r="C2" t="n">
-        <v>11878</v>
+        <v>8725</v>
       </c>
       <c r="D2" t="n">
-        <v>33693</v>
+        <v>27107</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2590</v>
+        <v>4109</v>
       </c>
       <c r="C3" t="n">
-        <v>9618</v>
+        <v>5360</v>
       </c>
       <c r="D3" t="n">
-        <v>13670</v>
+        <v>12919</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2128</v>
+        <v>2889</v>
       </c>
       <c r="C4" t="n">
-        <v>6510</v>
+        <v>5578</v>
       </c>
       <c r="D4" t="n">
-        <v>6006</v>
+        <v>6883</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1595</v>
+        <v>2118</v>
       </c>
       <c r="C5" t="n">
-        <v>6686</v>
+        <v>4646</v>
       </c>
       <c r="D5" t="n">
-        <v>2332</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>968</v>
+        <v>1350</v>
       </c>
       <c r="C6" t="n">
-        <v>5456</v>
+        <v>3499</v>
       </c>
       <c r="D6" t="n">
-        <v>1106</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>489</v>
+        <v>690</v>
       </c>
       <c r="C7" t="n">
-        <v>3695</v>
+        <v>2123</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>207</v>
+        <v>281</v>
       </c>
       <c r="C8" t="n">
-        <v>1968</v>
+        <v>1027</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C9" t="n">
-        <v>838</v>
+        <v>447</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>327</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5038</v>
+        <v>11934</v>
       </c>
       <c r="C2" t="n">
-        <v>12968</v>
+        <v>8050</v>
       </c>
       <c r="D2" t="n">
-        <v>30229</v>
+        <v>20919</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2878</v>
+        <v>5156</v>
       </c>
       <c r="C3" t="n">
-        <v>9346</v>
+        <v>6007</v>
       </c>
       <c r="D3" t="n">
-        <v>15059</v>
+        <v>13887</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1968</v>
+        <v>2891</v>
       </c>
       <c r="C4" t="n">
-        <v>7565</v>
+        <v>5363</v>
       </c>
       <c r="D4" t="n">
-        <v>6795</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1603</v>
+        <v>2168</v>
       </c>
       <c r="C5" t="n">
-        <v>6477</v>
+        <v>4907</v>
       </c>
       <c r="D5" t="n">
-        <v>2754</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1094</v>
+        <v>1534</v>
       </c>
       <c r="C6" t="n">
-        <v>5818</v>
+        <v>3917</v>
       </c>
       <c r="D6" t="n">
-        <v>1234</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>597</v>
+        <v>857</v>
       </c>
       <c r="C7" t="n">
-        <v>4313</v>
+        <v>2701</v>
       </c>
       <c r="D7" t="n">
-        <v>710</v>
+        <v>766</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>275</v>
+        <v>390</v>
       </c>
       <c r="C8" t="n">
-        <v>2574</v>
+        <v>1456</v>
       </c>
       <c r="D8" t="n">
-        <v>468</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="C9" t="n">
-        <v>1236</v>
+        <v>674</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>493</v>
+        <v>314</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4746</v>
+        <v>10612</v>
       </c>
       <c r="C2" t="n">
-        <v>9233</v>
+        <v>5409</v>
       </c>
       <c r="D2" t="n">
-        <v>25050</v>
+        <v>17101</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3417</v>
+        <v>5801</v>
       </c>
       <c r="C3" t="n">
-        <v>13454</v>
+        <v>8907</v>
       </c>
       <c r="D3" t="n">
-        <v>15741</v>
+        <v>15227</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1481</v>
+        <v>2003</v>
       </c>
       <c r="C4" t="n">
-        <v>10139</v>
+        <v>7748</v>
       </c>
       <c r="D4" t="n">
-        <v>6300</v>
+        <v>7319</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1010</v>
+        <v>1417</v>
       </c>
       <c r="C5" t="n">
-        <v>5701</v>
+        <v>3838</v>
       </c>
       <c r="D5" t="n">
-        <v>1923</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>551</v>
+        <v>791</v>
       </c>
       <c r="C6" t="n">
-        <v>4226</v>
+        <v>2646</v>
       </c>
       <c r="D6" t="n">
-        <v>695</v>
+        <v>750</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>360</v>
       </c>
       <c r="C7" t="n">
-        <v>2522</v>
+        <v>1426</v>
       </c>
       <c r="D7" t="n">
-        <v>458</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="C8" t="n">
-        <v>1211</v>
+        <v>660</v>
       </c>
       <c r="D8" t="n">
-        <v>314</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>483</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>49</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2884</v>
+        <v>6140</v>
       </c>
       <c r="C2" t="n">
-        <v>4314</v>
+        <v>3036</v>
       </c>
       <c r="D2" t="n">
-        <v>18257</v>
+        <v>11530</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3422</v>
+        <v>6693</v>
       </c>
       <c r="C3" t="n">
-        <v>10593</v>
+        <v>6568</v>
       </c>
       <c r="D3" t="n">
-        <v>16051</v>
+        <v>14741</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1903</v>
+        <v>2992</v>
       </c>
       <c r="C4" t="n">
-        <v>11781</v>
+        <v>8440</v>
       </c>
       <c r="D4" t="n">
-        <v>7588</v>
+        <v>8451</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1120</v>
+        <v>1569</v>
       </c>
       <c r="C5" t="n">
-        <v>7560</v>
+        <v>5593</v>
       </c>
       <c r="D5" t="n">
-        <v>2405</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>642</v>
+        <v>947</v>
       </c>
       <c r="C6" t="n">
-        <v>4912</v>
+        <v>3204</v>
       </c>
       <c r="D6" t="n">
-        <v>813</v>
+        <v>918</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>237</v>
+        <v>341</v>
       </c>
       <c r="C7" t="n">
-        <v>3160</v>
+        <v>1897</v>
       </c>
       <c r="D7" t="n">
-        <v>498</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>1568</v>
+        <v>884</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>503</v>
+        <v>367</v>
       </c>
       <c r="D9" t="n">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2557</v>
+        <v>6616</v>
       </c>
       <c r="C2" t="n">
-        <v>6452</v>
+        <v>7105</v>
       </c>
       <c r="D2" t="n">
-        <v>18006</v>
+        <v>10587</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2701</v>
+        <v>5411</v>
       </c>
       <c r="C3" t="n">
-        <v>6979</v>
+        <v>4250</v>
       </c>
       <c r="D3" t="n">
-        <v>15280</v>
+        <v>13264</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2174</v>
+        <v>3981</v>
       </c>
       <c r="C4" t="n">
-        <v>10988</v>
+        <v>7392</v>
       </c>
       <c r="D4" t="n">
-        <v>8657</v>
+        <v>9281</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1277</v>
+        <v>1933</v>
       </c>
       <c r="C5" t="n">
-        <v>9266</v>
+        <v>6843</v>
       </c>
       <c r="D5" t="n">
-        <v>3078</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>756</v>
+        <v>1113</v>
       </c>
       <c r="C6" t="n">
-        <v>6033</v>
+        <v>4304</v>
       </c>
       <c r="D6" t="n">
-        <v>1016</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>340</v>
+        <v>518</v>
       </c>
       <c r="C7" t="n">
-        <v>3862</v>
+        <v>2491</v>
       </c>
       <c r="D7" t="n">
-        <v>533</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="C8" t="n">
-        <v>2191</v>
+        <v>1309</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>888</v>
+        <v>568</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>321</v>
+        <v>276</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1562</v>
+        <v>3874</v>
       </c>
       <c r="C2" t="n">
-        <v>3188</v>
+        <v>3249</v>
       </c>
       <c r="D2" t="n">
-        <v>12704</v>
+        <v>7310</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2579</v>
+        <v>5506</v>
       </c>
       <c r="C3" t="n">
-        <v>6635</v>
+        <v>5096</v>
       </c>
       <c r="D3" t="n">
-        <v>15223</v>
+        <v>12645</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2376</v>
+        <v>4422</v>
       </c>
       <c r="C4" t="n">
-        <v>10621</v>
+        <v>6892</v>
       </c>
       <c r="D4" t="n">
-        <v>9377</v>
+        <v>9826</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1320</v>
+        <v>2012</v>
       </c>
       <c r="C5" t="n">
-        <v>11253</v>
+        <v>7910</v>
       </c>
       <c r="D5" t="n">
-        <v>3181</v>
+        <v>4089</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>600</v>
+        <v>941</v>
       </c>
       <c r="C6" t="n">
-        <v>6882</v>
+        <v>5265</v>
       </c>
       <c r="D6" t="n">
-        <v>1012</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>4006</v>
+        <v>2556</v>
       </c>
       <c r="D7" t="n">
-        <v>536</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1471</v>
+        <v>967</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>314</v>
+        <v>270</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1470</v>
+        <v>4355</v>
       </c>
       <c r="C2" t="n">
-        <v>8258</v>
+        <v>7251</v>
       </c>
       <c r="D2" t="n">
-        <v>10338</v>
+        <v>12632</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1871</v>
+        <v>4116</v>
       </c>
       <c r="C3" t="n">
-        <v>4638</v>
+        <v>3771</v>
       </c>
       <c r="D3" t="n">
-        <v>14048</v>
+        <v>11069</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2169</v>
+        <v>4249</v>
       </c>
       <c r="C4" t="n">
-        <v>8639</v>
+        <v>5886</v>
       </c>
       <c r="D4" t="n">
-        <v>9933</v>
+        <v>9987</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1534</v>
+        <v>2639</v>
       </c>
       <c r="C5" t="n">
-        <v>10860</v>
+        <v>7352</v>
       </c>
       <c r="D5" t="n">
-        <v>3917</v>
+        <v>4845</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>769</v>
+        <v>1239</v>
       </c>
       <c r="C6" t="n">
-        <v>8610</v>
+        <v>6409</v>
       </c>
       <c r="D6" t="n">
-        <v>1269</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>220</v>
+        <v>358</v>
       </c>
       <c r="C7" t="n">
-        <v>5153</v>
+        <v>3720</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>2343</v>
+        <v>1577</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>663</v>
+        <v>510</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>937</v>
+        <v>3204</v>
       </c>
       <c r="C2" t="n">
-        <v>5599</v>
+        <v>3796</v>
       </c>
       <c r="D2" t="n">
-        <v>9041</v>
+        <v>8988</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1535</v>
+        <v>3673</v>
       </c>
       <c r="C3" t="n">
-        <v>5490</v>
+        <v>4731</v>
       </c>
       <c r="D3" t="n">
-        <v>12890</v>
+        <v>10654</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1924</v>
+        <v>3874</v>
       </c>
       <c r="C4" t="n">
-        <v>7210</v>
+        <v>5003</v>
       </c>
       <c r="D4" t="n">
-        <v>10335</v>
+        <v>9924</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1645</v>
+        <v>2929</v>
       </c>
       <c r="C5" t="n">
-        <v>10221</v>
+        <v>6932</v>
       </c>
       <c r="D5" t="n">
-        <v>4413</v>
+        <v>5383</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>872</v>
+        <v>1497</v>
       </c>
       <c r="C6" t="n">
-        <v>9604</v>
+        <v>6976</v>
       </c>
       <c r="D6" t="n">
-        <v>1482</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>196</v>
+        <v>336</v>
       </c>
       <c r="C7" t="n">
-        <v>6249</v>
+        <v>4658</v>
       </c>
       <c r="D7" t="n">
-        <v>656</v>
+        <v>731</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>2952</v>
+        <v>2092</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>701</v>
+        <v>616</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1280</v>
+        <v>5635</v>
       </c>
       <c r="C2" t="n">
-        <v>13775</v>
+        <v>10243</v>
       </c>
       <c r="D2" t="n">
-        <v>8754</v>
+        <v>9871</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1131</v>
+        <v>2945</v>
       </c>
       <c r="C3" t="n">
-        <v>4946</v>
+        <v>3894</v>
       </c>
       <c r="D3" t="n">
-        <v>11654</v>
+        <v>9772</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1562</v>
+        <v>3336</v>
       </c>
       <c r="C4" t="n">
-        <v>6383</v>
+        <v>4781</v>
       </c>
       <c r="D4" t="n">
-        <v>10364</v>
+        <v>9727</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1587</v>
+        <v>2962</v>
       </c>
       <c r="C5" t="n">
-        <v>8881</v>
+        <v>5991</v>
       </c>
       <c r="D5" t="n">
-        <v>5017</v>
+        <v>5777</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1037</v>
+        <v>1848</v>
       </c>
       <c r="C6" t="n">
-        <v>9748</v>
+        <v>6898</v>
       </c>
       <c r="D6" t="n">
-        <v>1786</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>348</v>
+        <v>630</v>
       </c>
       <c r="C7" t="n">
-        <v>7397</v>
+        <v>5542</v>
       </c>
       <c r="D7" t="n">
-        <v>746</v>
+        <v>873</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>4045</v>
+        <v>3042</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1362</v>
+        <v>1113</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>40</v>
+      </c>
+      <c r="D14" t="n">
         <v>38</v>
-      </c>
-      <c r="D14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4425</v>
+        <v>4972</v>
       </c>
       <c r="C2" t="n">
-        <v>14029</v>
+        <v>2971</v>
       </c>
       <c r="D2" t="n">
-        <v>7527</v>
+        <v>7032</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>945</v>
+        <v>3987</v>
       </c>
       <c r="C2" t="n">
-        <v>8265</v>
+        <v>5818</v>
       </c>
       <c r="D2" t="n">
-        <v>6583</v>
+        <v>7265</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1577</v>
+        <v>4101</v>
       </c>
       <c r="C3" t="n">
-        <v>7293</v>
+        <v>5703</v>
       </c>
       <c r="D3" t="n">
-        <v>12403</v>
+        <v>10666</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2264</v>
+        <v>4445</v>
       </c>
       <c r="C4" t="n">
-        <v>9406</v>
+        <v>6841</v>
       </c>
       <c r="D4" t="n">
-        <v>10405</v>
+        <v>10015</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>958</v>
+        <v>1789</v>
       </c>
       <c r="C5" t="n">
-        <v>13385</v>
+        <v>9251</v>
       </c>
       <c r="D5" t="n">
-        <v>4456</v>
+        <v>5366</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>321</v>
+        <v>582</v>
       </c>
       <c r="C6" t="n">
-        <v>8873</v>
+        <v>6850</v>
       </c>
       <c r="D6" t="n">
-        <v>1500</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>3964</v>
+        <v>2981</v>
       </c>
       <c r="D7" t="n">
-        <v>485</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1334</v>
+        <v>1090</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="D9" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D10" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>39</v>
+      </c>
+      <c r="D13" t="n">
         <v>37</v>
-      </c>
-      <c r="D13" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5655</v>
+        <v>6495</v>
       </c>
       <c r="C2" t="n">
-        <v>8440</v>
+        <v>5702</v>
       </c>
       <c r="D2" t="n">
-        <v>8048</v>
+        <v>9110</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1881</v>
+        <v>2113</v>
       </c>
       <c r="C3" t="n">
-        <v>7070</v>
+        <v>1521</v>
       </c>
       <c r="D3" t="n">
-        <v>1903</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3986</v>
+        <v>5928</v>
       </c>
       <c r="C2" t="n">
-        <v>11354</v>
+        <v>6824</v>
       </c>
       <c r="D2" t="n">
-        <v>12210</v>
+        <v>20907</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3092</v>
+        <v>3584</v>
       </c>
       <c r="C3" t="n">
-        <v>6765</v>
+        <v>3383</v>
       </c>
       <c r="D3" t="n">
-        <v>2795</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>851</v>
+        <v>951</v>
       </c>
       <c r="C4" t="n">
-        <v>4186</v>
+        <v>949</v>
       </c>
       <c r="D4" t="n">
-        <v>1564</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5008,7 +5008,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4429</v>
+        <v>5264</v>
       </c>
       <c r="C2" t="n">
-        <v>9778</v>
+        <v>5756</v>
       </c>
       <c r="D2" t="n">
-        <v>12711</v>
+        <v>19582</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2906</v>
+        <v>3897</v>
       </c>
       <c r="C3" t="n">
-        <v>8086</v>
+        <v>4607</v>
       </c>
       <c r="D3" t="n">
-        <v>4100</v>
+        <v>5613</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1675</v>
+        <v>1948</v>
       </c>
       <c r="C4" t="n">
-        <v>5494</v>
+        <v>2298</v>
       </c>
       <c r="D4" t="n">
-        <v>1752</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>403</v>
+        <v>451</v>
       </c>
       <c r="C5" t="n">
-        <v>2385</v>
+        <v>621</v>
       </c>
       <c r="D5" t="n">
-        <v>1216</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>116</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4468</v>
+        <v>5764</v>
       </c>
       <c r="C2" t="n">
-        <v>10824</v>
+        <v>8509</v>
       </c>
       <c r="D2" t="n">
-        <v>24478</v>
+        <v>19944</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2966</v>
+        <v>3781</v>
       </c>
       <c r="C3" t="n">
-        <v>7795</v>
+        <v>4526</v>
       </c>
       <c r="D3" t="n">
-        <v>5120</v>
+        <v>7341</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1923</v>
+        <v>2456</v>
       </c>
       <c r="C4" t="n">
-        <v>6695</v>
+        <v>3513</v>
       </c>
       <c r="D4" t="n">
-        <v>2127</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>854</v>
+        <v>996</v>
       </c>
       <c r="C5" t="n">
-        <v>3947</v>
+        <v>1487</v>
       </c>
       <c r="D5" t="n">
-        <v>1259</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="C6" t="n">
-        <v>1339</v>
+        <v>464</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>942</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
         <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5537</v>
+        <v>7236</v>
       </c>
       <c r="C2" t="n">
-        <v>12028</v>
+        <v>7878</v>
       </c>
       <c r="D2" t="n">
-        <v>22123</v>
+        <v>27069</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2672</v>
+        <v>3468</v>
       </c>
       <c r="C3" t="n">
-        <v>7634</v>
+        <v>5403</v>
       </c>
       <c r="D3" t="n">
-        <v>7244</v>
+        <v>8222</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1497</v>
+        <v>1935</v>
       </c>
       <c r="C4" t="n">
-        <v>5964</v>
+        <v>3347</v>
       </c>
       <c r="D4" t="n">
-        <v>2274</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>722</v>
+        <v>908</v>
       </c>
       <c r="C5" t="n">
-        <v>3872</v>
+        <v>1862</v>
       </c>
       <c r="D5" t="n">
-        <v>1110</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>298</v>
       </c>
       <c r="C6" t="n">
-        <v>1769</v>
+        <v>666</v>
       </c>
       <c r="D6" t="n">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>523</v>
+        <v>260</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
         <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4488</v>
+        <v>5186</v>
       </c>
       <c r="C2" t="n">
-        <v>7763</v>
+        <v>6066</v>
       </c>
       <c r="D2" t="n">
-        <v>21397</v>
+        <v>22126</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3418</v>
+        <v>4485</v>
       </c>
       <c r="C3" t="n">
-        <v>8750</v>
+        <v>5911</v>
       </c>
       <c r="D3" t="n">
-        <v>9210</v>
+        <v>10920</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1798</v>
+        <v>2386</v>
       </c>
       <c r="C4" t="n">
-        <v>6833</v>
+        <v>4560</v>
       </c>
       <c r="D4" t="n">
-        <v>3206</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>984</v>
+        <v>1276</v>
       </c>
       <c r="C5" t="n">
-        <v>4996</v>
+        <v>2721</v>
       </c>
       <c r="D5" t="n">
-        <v>1289</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>444</v>
+        <v>559</v>
       </c>
       <c r="C6" t="n">
-        <v>2918</v>
+        <v>1357</v>
       </c>
       <c r="D6" t="n">
-        <v>810</v>
+        <v>827</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>1206</v>
+        <v>494</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,10 +6238,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3577</v>
+        <v>5361</v>
       </c>
       <c r="C2" t="n">
-        <v>6278</v>
+        <v>9386</v>
       </c>
       <c r="D2" t="n">
-        <v>25628</v>
+        <v>18765</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3230</v>
+        <v>3985</v>
       </c>
       <c r="C3" t="n">
-        <v>7151</v>
+        <v>5181</v>
       </c>
       <c r="D3" t="n">
-        <v>10414</v>
+        <v>11926</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2195</v>
+        <v>2947</v>
       </c>
       <c r="C4" t="n">
-        <v>7739</v>
+        <v>5243</v>
       </c>
       <c r="D4" t="n">
-        <v>4172</v>
+        <v>5057</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1213</v>
+        <v>1620</v>
       </c>
       <c r="C5" t="n">
-        <v>5862</v>
+        <v>3662</v>
       </c>
       <c r="D5" t="n">
-        <v>1599</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>633</v>
+        <v>833</v>
       </c>
       <c r="C6" t="n">
-        <v>3914</v>
+        <v>2087</v>
       </c>
       <c r="D6" t="n">
-        <v>873</v>
+        <v>921</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="C7" t="n">
-        <v>2077</v>
+        <v>958</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>784</v>
+        <v>373</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>287</v>
+        <v>227</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
         <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_8_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_8_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6512</v>
+        <v>1336</v>
       </c>
       <c r="C2" t="n">
-        <v>5768</v>
+        <v>1704</v>
       </c>
       <c r="D2" t="n">
-        <v>23958</v>
+        <v>18638</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3849</v>
+        <v>2013</v>
       </c>
       <c r="C3" t="n">
-        <v>6393</v>
+        <v>4763</v>
       </c>
       <c r="D3" t="n">
-        <v>12125</v>
+        <v>19757</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2942</v>
+        <v>1298</v>
       </c>
       <c r="C4" t="n">
-        <v>5100</v>
+        <v>7096</v>
       </c>
       <c r="D4" t="n">
-        <v>6156</v>
+        <v>8687</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1968</v>
+        <v>719</v>
       </c>
       <c r="C5" t="n">
-        <v>4405</v>
+        <v>4697</v>
       </c>
       <c r="D5" t="n">
-        <v>2345</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1105</v>
+        <v>305</v>
       </c>
       <c r="C6" t="n">
-        <v>2830</v>
+        <v>1740</v>
       </c>
       <c r="D6" t="n">
-        <v>1072</v>
+        <v>759</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>502</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>1521</v>
+        <v>663</v>
       </c>
       <c r="D7" t="n">
-        <v>647</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>185</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>650</v>
+        <v>347</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9681</v>
+        <v>1763</v>
       </c>
       <c r="C2" t="n">
-        <v>8725</v>
+        <v>4978</v>
       </c>
       <c r="D2" t="n">
-        <v>27107</v>
+        <v>15709</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4109</v>
+        <v>1428</v>
       </c>
       <c r="C3" t="n">
-        <v>5360</v>
+        <v>2788</v>
       </c>
       <c r="D3" t="n">
-        <v>12919</v>
+        <v>18196</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2889</v>
+        <v>1419</v>
       </c>
       <c r="C4" t="n">
-        <v>5578</v>
+        <v>5694</v>
       </c>
       <c r="D4" t="n">
-        <v>6883</v>
+        <v>10442</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2118</v>
+        <v>874</v>
       </c>
       <c r="C5" t="n">
-        <v>4646</v>
+        <v>5888</v>
       </c>
       <c r="D5" t="n">
-        <v>2895</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1350</v>
+        <v>446</v>
       </c>
       <c r="C6" t="n">
-        <v>3499</v>
+        <v>3186</v>
       </c>
       <c r="D6" t="n">
-        <v>1242</v>
+        <v>999</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>690</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>2123</v>
+        <v>1175</v>
       </c>
       <c r="D7" t="n">
-        <v>707</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1027</v>
+        <v>489</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>447</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11934</v>
+        <v>932</v>
       </c>
       <c r="C2" t="n">
-        <v>8050</v>
+        <v>2082</v>
       </c>
       <c r="D2" t="n">
-        <v>20919</v>
+        <v>10755</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5156</v>
+        <v>1465</v>
       </c>
       <c r="C3" t="n">
-        <v>6007</v>
+        <v>3517</v>
       </c>
       <c r="D3" t="n">
-        <v>13887</v>
+        <v>17431</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2891</v>
+        <v>1569</v>
       </c>
       <c r="C4" t="n">
-        <v>5363</v>
+        <v>5006</v>
       </c>
       <c r="D4" t="n">
-        <v>7600</v>
+        <v>11444</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2168</v>
+        <v>892</v>
       </c>
       <c r="C5" t="n">
-        <v>4907</v>
+        <v>6561</v>
       </c>
       <c r="D5" t="n">
-        <v>3353</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1534</v>
+        <v>349</v>
       </c>
       <c r="C6" t="n">
-        <v>3917</v>
+        <v>4066</v>
       </c>
       <c r="D6" t="n">
-        <v>1463</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>857</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>2701</v>
+        <v>1135</v>
       </c>
       <c r="D7" t="n">
-        <v>766</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>390</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1456</v>
+        <v>478</v>
       </c>
       <c r="D8" t="n">
-        <v>489</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>149</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>674</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>336</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>314</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>201</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>210</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10612</v>
+        <v>1101</v>
       </c>
       <c r="C2" t="n">
-        <v>5409</v>
+        <v>4190</v>
       </c>
       <c r="D2" t="n">
-        <v>17101</v>
+        <v>12587</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5801</v>
+        <v>1041</v>
       </c>
       <c r="C3" t="n">
-        <v>8907</v>
+        <v>2452</v>
       </c>
       <c r="D3" t="n">
-        <v>15227</v>
+        <v>15356</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2003</v>
+        <v>1351</v>
       </c>
       <c r="C4" t="n">
-        <v>7748</v>
+        <v>4163</v>
       </c>
       <c r="D4" t="n">
-        <v>7319</v>
+        <v>12130</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1417</v>
+        <v>1062</v>
       </c>
       <c r="C5" t="n">
-        <v>3838</v>
+        <v>5711</v>
       </c>
       <c r="D5" t="n">
-        <v>2367</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>791</v>
+        <v>519</v>
       </c>
       <c r="C6" t="n">
-        <v>2646</v>
+        <v>5277</v>
       </c>
       <c r="D6" t="n">
-        <v>750</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>360</v>
+        <v>149</v>
       </c>
       <c r="C7" t="n">
-        <v>1426</v>
+        <v>2449</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>660</v>
+        <v>751</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6140</v>
+        <v>590</v>
       </c>
       <c r="C2" t="n">
-        <v>3036</v>
+        <v>2458</v>
       </c>
       <c r="D2" t="n">
-        <v>11530</v>
+        <v>10618</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6693</v>
+        <v>928</v>
       </c>
       <c r="C3" t="n">
-        <v>6568</v>
+        <v>2933</v>
       </c>
       <c r="D3" t="n">
-        <v>14741</v>
+        <v>14094</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2992</v>
+        <v>1150</v>
       </c>
       <c r="C4" t="n">
-        <v>8440</v>
+        <v>3407</v>
       </c>
       <c r="D4" t="n">
-        <v>8451</v>
+        <v>12489</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1569</v>
+        <v>1125</v>
       </c>
       <c r="C5" t="n">
-        <v>5593</v>
+        <v>5172</v>
       </c>
       <c r="D5" t="n">
-        <v>2958</v>
+        <v>5717</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>947</v>
+        <v>627</v>
       </c>
       <c r="C6" t="n">
-        <v>3204</v>
+        <v>5648</v>
       </c>
       <c r="D6" t="n">
-        <v>918</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>341</v>
+        <v>167</v>
       </c>
       <c r="C7" t="n">
-        <v>1897</v>
+        <v>3447</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>884</v>
+        <v>1173</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>367</v>
+        <v>426</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6616</v>
+        <v>898</v>
       </c>
       <c r="C2" t="n">
-        <v>7105</v>
+        <v>5070</v>
       </c>
       <c r="D2" t="n">
-        <v>10587</v>
+        <v>13535</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5411</v>
+        <v>664</v>
       </c>
       <c r="C3" t="n">
-        <v>4250</v>
+        <v>2410</v>
       </c>
       <c r="D3" t="n">
-        <v>13264</v>
+        <v>12674</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3981</v>
+        <v>931</v>
       </c>
       <c r="C4" t="n">
-        <v>7392</v>
+        <v>3108</v>
       </c>
       <c r="D4" t="n">
-        <v>9281</v>
+        <v>12371</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1933</v>
+        <v>1037</v>
       </c>
       <c r="C5" t="n">
-        <v>6843</v>
+        <v>4251</v>
       </c>
       <c r="D5" t="n">
-        <v>3764</v>
+        <v>6583</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1113</v>
+        <v>762</v>
       </c>
       <c r="C6" t="n">
-        <v>4304</v>
+        <v>5438</v>
       </c>
       <c r="D6" t="n">
-        <v>1219</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>518</v>
+        <v>300</v>
       </c>
       <c r="C7" t="n">
-        <v>2491</v>
+        <v>4373</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>830</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>1309</v>
+        <v>2097</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>568</v>
+        <v>708</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
+        <v>66</v>
+      </c>
+      <c r="D14" t="n">
         <v>55</v>
-      </c>
-      <c r="D14" t="n">
-        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3874</v>
+        <v>603</v>
       </c>
       <c r="C2" t="n">
-        <v>3249</v>
+        <v>2637</v>
       </c>
       <c r="D2" t="n">
-        <v>7310</v>
+        <v>9745</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5506</v>
+        <v>934</v>
       </c>
       <c r="C3" t="n">
-        <v>5096</v>
+        <v>3339</v>
       </c>
       <c r="D3" t="n">
-        <v>12645</v>
+        <v>13843</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4422</v>
+        <v>1420</v>
       </c>
       <c r="C4" t="n">
-        <v>6892</v>
+        <v>4478</v>
       </c>
       <c r="D4" t="n">
-        <v>9826</v>
+        <v>12735</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2012</v>
+        <v>780</v>
       </c>
       <c r="C5" t="n">
-        <v>7910</v>
+        <v>6976</v>
       </c>
       <c r="D5" t="n">
-        <v>4089</v>
+        <v>5975</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>941</v>
+        <v>277</v>
       </c>
       <c r="C6" t="n">
-        <v>5265</v>
+        <v>5617</v>
       </c>
       <c r="D6" t="n">
-        <v>1210</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="C7" t="n">
-        <v>2556</v>
+        <v>2055</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>967</v>
+        <v>693</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
+        <v>64</v>
+      </c>
+      <c r="D13" t="n">
         <v>53</v>
-      </c>
-      <c r="D13" t="n">
-        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4355</v>
+        <v>327</v>
       </c>
       <c r="C2" t="n">
-        <v>7251</v>
+        <v>2096</v>
       </c>
       <c r="D2" t="n">
-        <v>12632</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4116</v>
+        <v>670</v>
       </c>
       <c r="C3" t="n">
-        <v>3771</v>
+        <v>2637</v>
       </c>
       <c r="D3" t="n">
-        <v>11069</v>
+        <v>12260</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4249</v>
+        <v>991</v>
       </c>
       <c r="C4" t="n">
-        <v>5886</v>
+        <v>3696</v>
       </c>
       <c r="D4" t="n">
-        <v>9987</v>
+        <v>12031</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2639</v>
+        <v>746</v>
       </c>
       <c r="C5" t="n">
-        <v>7352</v>
+        <v>5097</v>
       </c>
       <c r="D5" t="n">
-        <v>4845</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1239</v>
+        <v>277</v>
       </c>
       <c r="C6" t="n">
-        <v>6409</v>
+        <v>5164</v>
       </c>
       <c r="D6" t="n">
-        <v>1620</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>358</v>
+        <v>63</v>
       </c>
       <c r="C7" t="n">
-        <v>3720</v>
+        <v>2592</v>
       </c>
       <c r="D7" t="n">
-        <v>654</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1577</v>
+        <v>794</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>510</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>126</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3204</v>
+        <v>766</v>
       </c>
       <c r="C2" t="n">
-        <v>3796</v>
+        <v>6106</v>
       </c>
       <c r="D2" t="n">
-        <v>8988</v>
+        <v>15972</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3673</v>
+        <v>425</v>
       </c>
       <c r="C3" t="n">
-        <v>4731</v>
+        <v>2027</v>
       </c>
       <c r="D3" t="n">
-        <v>10654</v>
+        <v>10530</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3874</v>
+        <v>738</v>
       </c>
       <c r="C4" t="n">
-        <v>5003</v>
+        <v>3054</v>
       </c>
       <c r="D4" t="n">
-        <v>9924</v>
+        <v>11709</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2929</v>
+        <v>772</v>
       </c>
       <c r="C5" t="n">
-        <v>6932</v>
+        <v>4237</v>
       </c>
       <c r="D5" t="n">
-        <v>5383</v>
+        <v>7121</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1497</v>
+        <v>449</v>
       </c>
       <c r="C6" t="n">
-        <v>6976</v>
+        <v>5122</v>
       </c>
       <c r="D6" t="n">
-        <v>1910</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>336</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>4658</v>
+        <v>3901</v>
       </c>
       <c r="D7" t="n">
-        <v>731</v>
+        <v>848</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>2092</v>
+        <v>1639</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>616</v>
+        <v>512</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5635</v>
+        <v>1054</v>
       </c>
       <c r="C2" t="n">
-        <v>10243</v>
+        <v>4460</v>
       </c>
       <c r="D2" t="n">
-        <v>9871</v>
+        <v>16039</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2945</v>
+        <v>474</v>
       </c>
       <c r="C3" t="n">
-        <v>3894</v>
+        <v>3532</v>
       </c>
       <c r="D3" t="n">
-        <v>9772</v>
+        <v>10589</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3336</v>
+        <v>521</v>
       </c>
       <c r="C4" t="n">
-        <v>4781</v>
+        <v>2458</v>
       </c>
       <c r="D4" t="n">
-        <v>9727</v>
+        <v>11036</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2962</v>
+        <v>691</v>
       </c>
       <c r="C5" t="n">
-        <v>5991</v>
+        <v>3558</v>
       </c>
       <c r="D5" t="n">
-        <v>5777</v>
+        <v>7697</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1848</v>
+        <v>541</v>
       </c>
       <c r="C6" t="n">
-        <v>6898</v>
+        <v>4643</v>
       </c>
       <c r="D6" t="n">
-        <v>2351</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>630</v>
+        <v>245</v>
       </c>
       <c r="C7" t="n">
-        <v>5542</v>
+        <v>4435</v>
       </c>
       <c r="D7" t="n">
-        <v>873</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>3042</v>
+        <v>2680</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1113</v>
+        <v>1008</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4972</v>
+        <v>5197</v>
       </c>
       <c r="C2" t="n">
-        <v>2971</v>
+        <v>9232</v>
       </c>
       <c r="D2" t="n">
-        <v>7032</v>
+        <v>8922</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3987</v>
+        <v>989</v>
       </c>
       <c r="C2" t="n">
-        <v>5818</v>
+        <v>12537</v>
       </c>
       <c r="D2" t="n">
-        <v>7265</v>
+        <v>21067</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4101</v>
+        <v>583</v>
       </c>
       <c r="C3" t="n">
-        <v>5703</v>
+        <v>3479</v>
       </c>
       <c r="D3" t="n">
-        <v>10666</v>
+        <v>10618</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4445</v>
+        <v>431</v>
       </c>
       <c r="C4" t="n">
-        <v>6841</v>
+        <v>2922</v>
       </c>
       <c r="D4" t="n">
-        <v>10015</v>
+        <v>10627</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1789</v>
+        <v>573</v>
       </c>
       <c r="C5" t="n">
-        <v>9251</v>
+        <v>2977</v>
       </c>
       <c r="D5" t="n">
-        <v>5366</v>
+        <v>7901</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="C6" t="n">
-        <v>6850</v>
+        <v>4073</v>
       </c>
       <c r="D6" t="n">
-        <v>1896</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>332</v>
       </c>
       <c r="C7" t="n">
-        <v>2981</v>
+        <v>4524</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>1090</v>
+        <v>3418</v>
       </c>
       <c r="D8" t="n">
-        <v>304</v>
+        <v>532</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>338</v>
+        <v>1669</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
+        <v>591</v>
+      </c>
+      <c r="D10" t="n">
         <v>158</v>
-      </c>
-      <c r="D10" t="n">
-        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>62</v>
+      </c>
+      <c r="D13" t="n">
         <v>39</v>
-      </c>
-      <c r="D13" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6495</v>
+        <v>5049</v>
       </c>
       <c r="C2" t="n">
-        <v>5702</v>
+        <v>7448</v>
       </c>
       <c r="D2" t="n">
-        <v>9110</v>
+        <v>31238</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2113</v>
+        <v>1716</v>
       </c>
       <c r="C3" t="n">
-        <v>1521</v>
+        <v>3645</v>
       </c>
       <c r="D3" t="n">
-        <v>1876</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5928</v>
+        <v>2904</v>
       </c>
       <c r="C2" t="n">
-        <v>6824</v>
+        <v>7119</v>
       </c>
       <c r="D2" t="n">
-        <v>20907</v>
+        <v>33705</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3584</v>
+        <v>2853</v>
       </c>
       <c r="C3" t="n">
-        <v>3383</v>
+        <v>5097</v>
       </c>
       <c r="D3" t="n">
-        <v>2953</v>
+        <v>6873</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>951</v>
+        <v>818</v>
       </c>
       <c r="C4" t="n">
-        <v>949</v>
+        <v>2323</v>
       </c>
       <c r="D4" t="n">
-        <v>1559</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5264</v>
+        <v>1775</v>
       </c>
       <c r="C2" t="n">
-        <v>5756</v>
+        <v>7290</v>
       </c>
       <c r="D2" t="n">
-        <v>19582</v>
+        <v>31850</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3897</v>
+        <v>2399</v>
       </c>
       <c r="C3" t="n">
-        <v>4607</v>
+        <v>5390</v>
       </c>
       <c r="D3" t="n">
-        <v>5613</v>
+        <v>10874</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1948</v>
+        <v>1588</v>
       </c>
       <c r="C4" t="n">
-        <v>2298</v>
+        <v>3925</v>
       </c>
       <c r="D4" t="n">
-        <v>1764</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>451</v>
+        <v>396</v>
       </c>
       <c r="C5" t="n">
-        <v>621</v>
+        <v>1421</v>
       </c>
       <c r="D5" t="n">
-        <v>1221</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5764</v>
+        <v>2016</v>
       </c>
       <c r="C2" t="n">
-        <v>8509</v>
+        <v>6217</v>
       </c>
       <c r="D2" t="n">
-        <v>19944</v>
+        <v>41249</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3781</v>
+        <v>1738</v>
       </c>
       <c r="C3" t="n">
-        <v>4526</v>
+        <v>5562</v>
       </c>
       <c r="D3" t="n">
-        <v>7341</v>
+        <v>13447</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2456</v>
+        <v>1718</v>
       </c>
       <c r="C4" t="n">
-        <v>3513</v>
+        <v>4673</v>
       </c>
       <c r="D4" t="n">
-        <v>2395</v>
+        <v>4051</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>996</v>
+        <v>833</v>
       </c>
       <c r="C5" t="n">
-        <v>1487</v>
+        <v>2761</v>
       </c>
       <c r="D5" t="n">
-        <v>1282</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>260</v>
+        <v>226</v>
       </c>
       <c r="C6" t="n">
-        <v>464</v>
+        <v>870</v>
       </c>
       <c r="D6" t="n">
-        <v>942</v>
+        <v>836</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>308</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7236</v>
+        <v>1719</v>
       </c>
       <c r="C2" t="n">
-        <v>7878</v>
+        <v>4916</v>
       </c>
       <c r="D2" t="n">
-        <v>27069</v>
+        <v>36005</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3468</v>
+        <v>1541</v>
       </c>
       <c r="C3" t="n">
-        <v>5403</v>
+        <v>5138</v>
       </c>
       <c r="D3" t="n">
-        <v>8222</v>
+        <v>16726</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1935</v>
+        <v>1500</v>
       </c>
       <c r="C4" t="n">
-        <v>3347</v>
+        <v>5045</v>
       </c>
       <c r="D4" t="n">
-        <v>2794</v>
+        <v>5641</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>908</v>
+        <v>1082</v>
       </c>
       <c r="C5" t="n">
-        <v>1862</v>
+        <v>3649</v>
       </c>
       <c r="D5" t="n">
-        <v>1172</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>298</v>
+        <v>454</v>
       </c>
       <c r="C6" t="n">
-        <v>666</v>
+        <v>1804</v>
       </c>
       <c r="D6" t="n">
-        <v>754</v>
+        <v>893</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>260</v>
+        <v>576</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5186</v>
+        <v>3070</v>
       </c>
       <c r="C2" t="n">
-        <v>6066</v>
+        <v>5596</v>
       </c>
       <c r="D2" t="n">
-        <v>22126</v>
+        <v>34327</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4485</v>
+        <v>1339</v>
       </c>
       <c r="C3" t="n">
-        <v>5911</v>
+        <v>4412</v>
       </c>
       <c r="D3" t="n">
-        <v>10920</v>
+        <v>18351</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2386</v>
+        <v>1305</v>
       </c>
       <c r="C4" t="n">
-        <v>4560</v>
+        <v>4986</v>
       </c>
       <c r="D4" t="n">
-        <v>3855</v>
+        <v>7385</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1276</v>
+        <v>1136</v>
       </c>
       <c r="C5" t="n">
-        <v>2721</v>
+        <v>4243</v>
       </c>
       <c r="D5" t="n">
-        <v>1452</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>559</v>
+        <v>655</v>
       </c>
       <c r="C6" t="n">
-        <v>1357</v>
+        <v>2618</v>
       </c>
       <c r="D6" t="n">
-        <v>827</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>178</v>
+        <v>247</v>
       </c>
       <c r="C7" t="n">
-        <v>494</v>
+        <v>1141</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5361</v>
+        <v>2684</v>
       </c>
       <c r="C2" t="n">
-        <v>9386</v>
+        <v>3491</v>
       </c>
       <c r="D2" t="n">
-        <v>18765</v>
+        <v>27264</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3985</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="n">
-        <v>5181</v>
+        <v>6943</v>
       </c>
       <c r="D3" t="n">
-        <v>11926</v>
+        <v>19869</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2947</v>
+        <v>1049</v>
       </c>
       <c r="C4" t="n">
-        <v>5243</v>
+        <v>7136</v>
       </c>
       <c r="D4" t="n">
-        <v>5057</v>
+        <v>6595</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1620</v>
+        <v>605</v>
       </c>
       <c r="C5" t="n">
-        <v>3662</v>
+        <v>2565</v>
       </c>
       <c r="D5" t="n">
-        <v>1869</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>833</v>
+        <v>228</v>
       </c>
       <c r="C6" t="n">
-        <v>2087</v>
+        <v>1118</v>
       </c>
       <c r="D6" t="n">
-        <v>921</v>
+        <v>642</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>329</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>958</v>
+        <v>413</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>373</v>
+        <v>277</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
